--- a/Bauernfeind_etal_2013/Bauernfeind_etal_2013_Table2_snapshot.xlsx
+++ b/Bauernfeind_etal_2013/Bauernfeind_etal_2013_Table2_snapshot.xlsx
@@ -1,428 +1,420 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/Bauernfeind_etal_2013/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_96A7A46CD957D6A79EA442F081F0E6F61FD5B359" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4635C70B-F920-CA43-A784-0CE090383803}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="47100" yWindow="-3420" windowWidth="22340" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Table2_snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Extraction_notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Table2_snapshot" sheetId="1" r:id="rId1"/>
+    <sheet name="Extraction_notes" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
-  <si>
-    <t xml:space="preserve">Table 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stereologic estimates of shrinkage-corrected volumes (cm^3) for right insula and its subdivisions in each human and great ape sampled.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volume estimates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">of right insular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subdivisions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Species</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Individual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granular Dysgranular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agranular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FI Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">insula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H9-88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapiens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H. sapiens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MU-88-65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SN207-84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W2-2-70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STD-IIA-54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pan paniscus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nambo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P. paniscus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCZ-2007-52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zahlia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA0171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">troglodytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P. troglodytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YN00-170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorilla gorilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">862094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G. gorilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YN82-140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pongo abelii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M00305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pongo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sabtu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pygmaeus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P. pygmaeus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Briggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">source_pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bauernfeind_etal_2013.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">printed_page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdf_page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extractor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pdftools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">table_area_top_left_bottom_right_pts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">548, 40, 741, 300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">column_separators_pts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89, 136, 171, 205, 237, 259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bauernfeind_etal_2013_Table2_snapshot.xlsx</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="129">
+  <si>
+    <t>Table 2</t>
+  </si>
+  <si>
+    <t>Stereologic estimates of shrinkage-corrected volumes (cm^3) for right insula and its subdivisions in each human and great ape sampled.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>Agranular</t>
+  </si>
+  <si>
+    <t>FI Total</t>
+  </si>
+  <si>
+    <t>insula</t>
+  </si>
+  <si>
+    <t>volume</t>
+  </si>
+  <si>
+    <t>H9-88</t>
+  </si>
+  <si>
+    <t>1.984</t>
+  </si>
+  <si>
+    <t>3.509</t>
+  </si>
+  <si>
+    <t>2.062</t>
+  </si>
+  <si>
+    <t>0.253</t>
+  </si>
+  <si>
+    <t>7.809</t>
+  </si>
+  <si>
+    <t>H. sapiens</t>
+  </si>
+  <si>
+    <t>MU-88-65</t>
+  </si>
+  <si>
+    <t>1.136</t>
+  </si>
+  <si>
+    <t>2.208</t>
+  </si>
+  <si>
+    <t>1.710</t>
+  </si>
+  <si>
+    <t>0.391</t>
+  </si>
+  <si>
+    <t>5.445</t>
+  </si>
+  <si>
+    <t>SN207-84</t>
+  </si>
+  <si>
+    <t>1.914</t>
+  </si>
+  <si>
+    <t>1.860</t>
+  </si>
+  <si>
+    <t>1.973</t>
+  </si>
+  <si>
+    <t>0.233</t>
+  </si>
+  <si>
+    <t>5.980</t>
+  </si>
+  <si>
+    <t>W2-2-70</t>
+  </si>
+  <si>
+    <t>1.456</t>
+  </si>
+  <si>
+    <t>3.638</t>
+  </si>
+  <si>
+    <t>1.653</t>
+  </si>
+  <si>
+    <t>0.509</t>
+  </si>
+  <si>
+    <t>7.255</t>
+  </si>
+  <si>
+    <t>STD-IIA-54</t>
+  </si>
+  <si>
+    <t>0.673</t>
+  </si>
+  <si>
+    <t>2.650</t>
+  </si>
+  <si>
+    <t>0.485</t>
+  </si>
+  <si>
+    <t>0.454</t>
+  </si>
+  <si>
+    <t>4.262</t>
+  </si>
+  <si>
+    <t>Pan paniscus</t>
+  </si>
+  <si>
+    <t>Nambo</t>
+  </si>
+  <si>
+    <t>0.310</t>
+  </si>
+  <si>
+    <t>0.728</t>
+  </si>
+  <si>
+    <t>0.394</t>
+  </si>
+  <si>
+    <t>0.199</t>
+  </si>
+  <si>
+    <t>1.631</t>
+  </si>
+  <si>
+    <t>P. paniscus</t>
+  </si>
+  <si>
+    <t>MCZ-2007-52</t>
+  </si>
+  <si>
+    <t>0.250</t>
+  </si>
+  <si>
+    <t>0.756</t>
+  </si>
+  <si>
+    <t>0.302</t>
+  </si>
+  <si>
+    <t>0.163</t>
+  </si>
+  <si>
+    <t>1.470</t>
+  </si>
+  <si>
+    <t>Zahlia</t>
+  </si>
+  <si>
+    <t>0.252</t>
+  </si>
+  <si>
+    <t>0.902</t>
+  </si>
+  <si>
+    <t>0.408</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>1.665</t>
+  </si>
+  <si>
+    <t>CA0171</t>
+  </si>
+  <si>
+    <t>0.346</t>
+  </si>
+  <si>
+    <t>0.816</t>
+  </si>
+  <si>
+    <t>0.160</t>
+  </si>
+  <si>
+    <t>0.146</t>
+  </si>
+  <si>
+    <t>1.468</t>
+  </si>
+  <si>
+    <t>P. troglodytes</t>
+  </si>
+  <si>
+    <t>YN00-170</t>
+  </si>
+  <si>
+    <t>0.585</t>
+  </si>
+  <si>
+    <t>0.366</t>
+  </si>
+  <si>
+    <t>0.155</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>1.188</t>
+  </si>
+  <si>
+    <t>Gorilla gorilla</t>
+  </si>
+  <si>
+    <t>862094</t>
+  </si>
+  <si>
+    <t>0.349</t>
+  </si>
+  <si>
+    <t>0.996</t>
+  </si>
+  <si>
+    <t>0.276</t>
+  </si>
+  <si>
+    <t>0.136</t>
+  </si>
+  <si>
+    <t>1.757</t>
+  </si>
+  <si>
+    <t>G. gorilla</t>
+  </si>
+  <si>
+    <t>YN82-140</t>
+  </si>
+  <si>
+    <t>0.282</t>
+  </si>
+  <si>
+    <t>0.933</t>
+  </si>
+  <si>
+    <t>0.798</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>2.084</t>
+  </si>
+  <si>
+    <t>Pongo abelii</t>
+  </si>
+  <si>
+    <t>M00305</t>
+  </si>
+  <si>
+    <t>0.186</t>
+  </si>
+  <si>
+    <t>0.652</t>
+  </si>
+  <si>
+    <t>0.361</t>
+  </si>
+  <si>
+    <t>0.000</t>
+  </si>
+  <si>
+    <t>1.199</t>
+  </si>
+  <si>
+    <t>Sabtu</t>
+  </si>
+  <si>
+    <t>0.313</t>
+  </si>
+  <si>
+    <t>0.997</t>
+  </si>
+  <si>
+    <t>0.474</t>
+  </si>
+  <si>
+    <t>1.784</t>
+  </si>
+  <si>
+    <t>P. pygmaeus</t>
+  </si>
+  <si>
+    <t>Briggs</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>0.637</t>
+  </si>
+  <si>
+    <t>0.654</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>1.446</t>
+  </si>
+  <si>
+    <t>field</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>source_pdf</t>
+  </si>
+  <si>
+    <t>bauernfeind_etal_2013.pdf</t>
+  </si>
+  <si>
+    <t>printed_page</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>pdf_page</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>extractor</t>
+  </si>
+  <si>
+    <t>pdftools</t>
+  </si>
+  <si>
+    <t>table_area_top_left_bottom_right_pts</t>
+  </si>
+  <si>
+    <t>548, 40, 741, 300</t>
+  </si>
+  <si>
+    <t>column_separators_pts</t>
+  </si>
+  <si>
+    <t>89, 136, 171, 205, 237, 259</t>
+  </si>
+  <si>
+    <t>output</t>
+  </si>
+  <si>
+    <t>Bauernfeind_etal_2013_Table2_snapshot.xlsx</t>
+  </si>
+  <si>
+    <t>Pongo pygmaeus</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>3 (cm)</t>
+  </si>
+  <si>
+    <t>Volume estimates of right insular subdivisions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granular </t>
+  </si>
+  <si>
+    <t>Dysgranular</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -458,6 +450,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -739,589 +740,520 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="G4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" t="s">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F5" t="s">
         <v>6</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G5" t="s">
         <v>7</v>
       </c>
-      <c r="G4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D7" t="s">
         <v>11</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E7" t="s">
         <v>12</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="G7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>17</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>18</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E8" t="s">
         <v>19</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F8" t="s">
         <v>20</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>25</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>26</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>27</v>
       </c>
-      <c r="F9" t="s">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="G9" t="s">
+      <c r="C10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
         <v>30</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>31</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>33</v>
       </c>
-      <c r="F10" t="s">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="G10" t="s">
+      <c r="C11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>36</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>37</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>38</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>39</v>
       </c>
-      <c r="F11" t="s">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>40</v>
       </c>
-      <c r="G11" t="s">
+      <c r="B12" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>43</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>44</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>45</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>46</v>
       </c>
-      <c r="G12" t="s">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>48</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>49</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>50</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>51</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>52</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>53</v>
       </c>
-      <c r="G13" t="s">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
+      <c r="C14" t="s">
         <v>55</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
         <v>56</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
         <v>57</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>58</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>59</v>
       </c>
-      <c r="F14" t="s">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" t="s">
         <v>60</v>
       </c>
-      <c r="G14" t="s">
+      <c r="C15" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>62</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>63</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>64</v>
       </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>65</v>
       </c>
-      <c r="F15" t="s">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>66</v>
       </c>
-      <c r="G15" t="s">
+      <c r="B16" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
+      <c r="C16" t="s">
         <v>68</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
         <v>69</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>70</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>71</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>72</v>
       </c>
-      <c r="F16" t="s">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>73</v>
       </c>
-      <c r="G16" t="s">
+      <c r="B17" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
+      <c r="C17" t="s">
         <v>75</v>
       </c>
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" t="s">
         <v>92</v>
       </c>
-      <c r="D20" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" t="s">
-        <v>94</v>
-      </c>
-      <c r="F20" t="s">
-        <v>95</v>
-      </c>
       <c r="G20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G21" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>104</v>
-      </c>
-      <c r="B22" t="s">
         <v>105</v>
-      </c>
-      <c r="C22" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" t="s">
-        <v>108</v>
-      </c>
-      <c r="F22" t="s">
-        <v>102</v>
-      </c>
-      <c r="G22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>110</v>
-      </c>
-      <c r="B23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>111</v>
-      </c>
-      <c r="B24" t="s">
-        <v>112</v>
-      </c>
-      <c r="C24" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" t="s">
-        <v>115</v>
-      </c>
-      <c r="F24" t="s">
-        <v>116</v>
-      </c>
-      <c r="G24" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="80.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="36.6640625" customWidth="1"/>
+    <col min="2" max="2" width="80.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>118</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>120</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B8" t="s">
         <v>121</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B8" t="s">
-        <v>133</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -1576,15 +1508,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1597,13 +1520,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{742AB410-4344-4E42-B06A-B839A54ED12B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59E1646E-04B3-4607-9407-1A0CBE304AE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59E1646E-04B3-4607-9407-1A0CBE304AE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{742AB410-4344-4E42-B06A-B839A54ED12B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F562C2A-856C-49B2-A27D-CB91F7CB02D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F562C2A-856C-49B2-A27D-CB91F7CB02D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>